--- a/accountant_forms/009_weekly_expense_calculation_form--accountant_forms.xlsx
+++ b/accountant_forms/009_weekly_expense_calculation_form--accountant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cny</t>
+          <t>hkd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>HKD</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hkd</t>
+          <t>chf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CHF</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chf</t>
+          <t>myr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>MYR</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>myr</t>
+          <t>twd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>TWD</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>twd</t>
+          <t>sgd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>SGD</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sgd</t>
+          <t>aed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>AED</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>aed</t>
+          <t>qar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>QAR</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qar</t>
+          <t>sar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QAR</t>
+          <t>SAR</t>
         </is>
       </c>
     </row>
@@ -1304,27 +1304,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sar</t>
+          <t>kwd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>currency_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>kwd</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>KWD</t>
         </is>
